--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="491">
   <si>
     <t/>
   </si>
@@ -355,12 +355,6 @@
     <t>11</t>
   </si>
   <si>
-    <t>10003144</t>
-  </si>
-  <si>
-    <t>MONDE BOURBON CHO140</t>
-  </si>
-  <si>
     <t>20142677</t>
   </si>
   <si>
@@ -1009,6 +1003,18 @@
     <t>NISSIN COCONUT 200GR</t>
   </si>
   <si>
+    <t>20143948</t>
+  </si>
+  <si>
+    <t>K/G ONE SNCK TOPKI50</t>
+  </si>
+  <si>
+    <t>20143947</t>
+  </si>
+  <si>
+    <t>K/G ONE SNCK BLGGI50</t>
+  </si>
+  <si>
     <t>20062816</t>
   </si>
   <si>
@@ -1061,6 +1067,12 @@
   </si>
   <si>
     <t>NISSIN COK.SG KJU110</t>
+  </si>
+  <si>
+    <t>20143950</t>
+  </si>
+  <si>
+    <t>K/G CZRNG CKS KEJU70</t>
   </si>
   <si>
     <t>20111641</t>
@@ -1864,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F218"/>
+  <dimension ref="A1:F220"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2868,7 +2880,7 @@
         <v>113</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2888,10 +2900,10 @@
         <v>113</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,30 +2917,30 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2945,10 +2957,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2965,10 +2977,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2985,13 +2997,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3005,30 +3017,30 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -3045,10 +3057,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -3065,10 +3077,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -3085,10 +3097,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -3096,19 +3108,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -3125,10 +3137,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -3145,10 +3157,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -3165,10 +3177,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -3185,10 +3197,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -3196,19 +3208,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -3225,10 +3237,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -3245,10 +3257,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -3265,10 +3277,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -3276,19 +3288,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -3305,10 +3317,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -3316,19 +3328,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -3345,13 +3357,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3365,10 +3377,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
@@ -3385,10 +3397,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
@@ -3405,10 +3417,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
@@ -3425,10 +3437,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
@@ -3445,33 +3457,33 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3485,10 +3497,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>13</v>
@@ -3505,13 +3517,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3525,10 +3537,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>6</v>
@@ -3545,10 +3557,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -3565,10 +3577,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -3585,10 +3597,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -3596,19 +3608,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -3625,10 +3637,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -3645,10 +3657,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -3665,10 +3677,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3676,19 +3688,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3705,10 +3717,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3725,10 +3737,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -3745,10 +3757,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3756,19 +3768,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3785,10 +3797,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -3805,10 +3817,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>6</v>
@@ -3816,19 +3828,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>6</v>
@@ -3845,10 +3857,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>6</v>
@@ -3865,10 +3877,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>6</v>
@@ -3876,19 +3888,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>6</v>
@@ -3905,10 +3917,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>6</v>
@@ -3925,10 +3937,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>6</v>
@@ -3945,10 +3957,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3965,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3985,10 +3997,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -4005,10 +4017,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -4025,10 +4037,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>6</v>
@@ -4036,19 +4048,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>6</v>
@@ -4065,10 +4077,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -4085,10 +4097,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -4105,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -4125,10 +4137,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -4145,10 +4157,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -4165,13 +4177,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4185,30 +4197,30 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -4225,10 +4237,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -4245,10 +4257,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -4265,10 +4277,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -4285,13 +4297,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4305,10 +4317,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>13</v>
@@ -4325,13 +4337,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4345,10 +4357,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -4365,10 +4377,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>6</v>
@@ -4385,10 +4397,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>6</v>
@@ -4396,19 +4408,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>6</v>
@@ -4425,10 +4437,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>6</v>
@@ -4445,10 +4457,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>6</v>
@@ -4465,10 +4477,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>6</v>
@@ -4485,10 +4497,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>6</v>
@@ -4505,10 +4517,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>6</v>
@@ -4525,10 +4537,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>6</v>
@@ -4545,10 +4557,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>6</v>
@@ -4565,10 +4577,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>6</v>
@@ -4585,10 +4597,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>6</v>
@@ -4596,19 +4608,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>6</v>
@@ -4625,10 +4637,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>6</v>
@@ -4645,13 +4657,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4665,13 +4677,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4685,10 +4697,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4705,10 +4717,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4716,19 +4728,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4745,13 +4757,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4765,13 +4777,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4785,10 +4797,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4805,10 +4817,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4816,19 +4828,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4845,10 +4857,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4865,10 +4877,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4876,19 +4888,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4905,10 +4917,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4925,13 +4937,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4945,30 +4957,30 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -4985,10 +4997,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>6</v>
@@ -5005,10 +5017,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>6</v>
@@ -5025,10 +5037,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>6</v>
@@ -5036,19 +5048,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>6</v>
@@ -5056,39 +5068,39 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>357</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>6</v>
@@ -5096,39 +5108,39 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>6</v>
@@ -5136,19 +5148,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>6</v>
@@ -5165,10 +5177,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>6</v>
@@ -5185,10 +5197,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>6</v>
@@ -5196,19 +5208,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>6</v>
@@ -5216,19 +5228,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E168" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>6</v>
@@ -5245,10 +5257,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>6</v>
@@ -5265,10 +5277,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>6</v>
@@ -5285,10 +5297,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>6</v>
@@ -5296,19 +5308,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>6</v>
@@ -5316,19 +5328,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>6</v>
@@ -5345,10 +5357,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>6</v>
@@ -5365,10 +5377,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>6</v>
@@ -5376,19 +5388,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>6</v>
@@ -5396,22 +5408,22 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5425,13 +5437,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5445,13 +5457,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5465,13 +5477,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5485,10 +5497,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>6</v>
@@ -5505,10 +5517,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>6</v>
@@ -5525,10 +5537,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>6</v>
@@ -5545,73 +5557,73 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>413</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F187" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5625,50 +5637,50 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>6</v>
@@ -5685,10 +5697,10 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>6</v>
@@ -5705,50 +5717,50 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>96</v>
@@ -5765,10 +5777,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>96</v>
@@ -5785,50 +5797,50 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>6</v>
@@ -5845,10 +5857,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>6</v>
@@ -5865,10 +5877,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>6</v>
@@ -5876,39 +5888,39 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>6</v>
@@ -5925,30 +5937,30 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>6</v>
@@ -5956,19 +5968,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="E205" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>6</v>
@@ -5985,10 +5997,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>6</v>
@@ -5996,19 +6008,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>463</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>6</v>
@@ -6016,19 +6028,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>6</v>
@@ -6045,10 +6057,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>6</v>
@@ -6065,10 +6077,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>6</v>
@@ -6085,10 +6097,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>6</v>
@@ -6105,10 +6117,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>6</v>
@@ -6125,10 +6137,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>6</v>
@@ -6136,19 +6148,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>6</v>
@@ -6156,19 +6168,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E215" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>6</v>
@@ -6185,10 +6197,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>6</v>
@@ -6205,10 +6217,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>6</v>
@@ -6225,12 +6237,52 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E218" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E220" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F218" s="1" t="s">
+      <c r="F220" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="493">
   <si>
     <t/>
   </si>
@@ -499,7 +499,13 @@
     <t>20138464</t>
   </si>
   <si>
-    <t>OREO ORIGINAL 147.2G</t>
+    <t>OREO ORIGINAL 140G</t>
+  </si>
+  <si>
+    <t>20143911</t>
+  </si>
+  <si>
+    <t>OREO KLAPA PANDAN105</t>
   </si>
   <si>
     <t>20143289</t>
@@ -838,19 +844,19 @@
     <t>10038704</t>
   </si>
   <si>
-    <t>MEIJI H/PANDA CHOC42</t>
+    <t>MEIJI H/P CHO 42 G</t>
   </si>
   <si>
     <t>10004490</t>
   </si>
   <si>
-    <t>HELLO PANDA STRW 42G</t>
+    <t>MEIJI H/P STRW 42 G</t>
   </si>
   <si>
     <t>20134559</t>
   </si>
   <si>
-    <t>HLO PANDA DB.CHO 42G</t>
+    <t>MEIJI H/P D.CHO 42 G</t>
   </si>
   <si>
     <t>20134875</t>
@@ -1420,7 +1426,7 @@
     <t>20103341</t>
   </si>
   <si>
-    <t>ROMA MLKS COK KLP 95</t>
+    <t>ROMA MLKS COK KLP 90</t>
   </si>
   <si>
     <t>20065096</t>
@@ -1876,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F220"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3317,10 +3323,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -3328,19 +3334,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -3357,13 +3363,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3377,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
@@ -3397,10 +3403,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
@@ -3417,10 +3423,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
@@ -3437,10 +3443,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
@@ -3457,33 +3463,33 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="E80" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3497,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>13</v>
@@ -3517,13 +3523,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3537,10 +3543,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>6</v>
@@ -3557,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -3577,10 +3583,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -3597,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -3608,19 +3614,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -3637,10 +3643,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -3657,10 +3663,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -3677,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3688,19 +3694,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3717,10 +3723,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3737,10 +3743,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -3757,10 +3763,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3768,19 +3774,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3797,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -3817,10 +3823,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>6</v>
@@ -3828,19 +3834,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>6</v>
@@ -3857,10 +3863,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>6</v>
@@ -3877,10 +3883,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>6</v>
@@ -3888,19 +3894,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>6</v>
@@ -3917,10 +3923,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>6</v>
@@ -3937,10 +3943,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>6</v>
@@ -3957,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3977,10 +3983,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3997,10 +4003,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -4017,10 +4023,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -4037,10 +4043,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>6</v>
@@ -4048,19 +4054,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>6</v>
@@ -4077,10 +4083,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -4097,10 +4103,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -4117,10 +4123,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -4137,10 +4143,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -4157,10 +4163,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -4177,13 +4183,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4197,30 +4203,30 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -4237,10 +4243,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -4257,10 +4263,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -4277,10 +4283,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -4297,13 +4303,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4317,10 +4323,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>13</v>
@@ -4337,13 +4343,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4357,10 +4363,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -4377,10 +4383,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>6</v>
@@ -4397,10 +4403,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>6</v>
@@ -4408,19 +4414,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>6</v>
@@ -4437,10 +4443,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>6</v>
@@ -4457,10 +4463,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>6</v>
@@ -4477,10 +4483,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>6</v>
@@ -4497,10 +4503,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>6</v>
@@ -4517,10 +4523,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>6</v>
@@ -4537,10 +4543,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>6</v>
@@ -4557,10 +4563,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>6</v>
@@ -4577,10 +4583,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>6</v>
@@ -4597,10 +4603,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>6</v>
@@ -4608,19 +4614,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>6</v>
@@ -4637,10 +4643,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>6</v>
@@ -4657,13 +4663,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4677,13 +4683,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4697,10 +4703,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4717,10 +4723,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4728,19 +4734,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4757,13 +4763,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4777,13 +4783,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4797,10 +4803,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4817,10 +4823,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4828,19 +4834,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4857,10 +4863,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4877,10 +4883,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4897,10 +4903,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4908,19 +4914,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4937,10 +4943,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4957,13 +4963,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4977,30 +4983,30 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>6</v>
@@ -5017,10 +5023,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>6</v>
@@ -5037,10 +5043,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>6</v>
@@ -5057,10 +5063,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>6</v>
@@ -5077,10 +5083,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>6</v>
@@ -5088,19 +5094,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E161" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>6</v>
@@ -5117,33 +5123,33 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>361</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5157,10 +5163,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>6</v>
@@ -5168,19 +5174,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>6</v>
@@ -5197,10 +5203,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>6</v>
@@ -5217,10 +5223,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>6</v>
@@ -5237,10 +5243,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>6</v>
@@ -5248,19 +5254,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>6</v>
@@ -5277,10 +5283,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>6</v>
@@ -5297,10 +5303,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>6</v>
@@ -5317,10 +5323,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>6</v>
@@ -5337,10 +5343,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>6</v>
@@ -5348,19 +5354,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>6</v>
@@ -5377,10 +5383,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>6</v>
@@ -5397,10 +5403,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>6</v>
@@ -5417,10 +5423,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>6</v>
@@ -5428,19 +5434,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>6</v>
@@ -5457,13 +5463,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5477,10 +5483,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>13</v>
@@ -5497,13 +5503,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5517,10 +5523,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>6</v>
@@ -5537,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>6</v>
@@ -5557,10 +5563,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>6</v>
@@ -5577,10 +5583,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>6</v>
@@ -5597,53 +5603,53 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>417</v>
+        <v>96</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F188" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5657,10 +5663,10 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>52</v>
@@ -5677,30 +5683,30 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>6</v>
@@ -5717,10 +5723,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>6</v>
@@ -5737,10 +5743,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>6</v>
@@ -5757,30 +5763,30 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="E195" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>96</v>
@@ -5797,10 +5803,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>96</v>
@@ -5817,10 +5823,10 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>96</v>
@@ -5837,30 +5843,30 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="E199" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>6</v>
@@ -5877,10 +5883,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>6</v>
@@ -5897,10 +5903,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>6</v>
@@ -5917,10 +5923,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>6</v>
@@ -5928,22 +5934,22 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="E203" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -5957,13 +5963,13 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5977,10 +5983,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>6</v>
@@ -5988,19 +5994,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="E206" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>6</v>
@@ -6017,10 +6023,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>6</v>
@@ -6037,10 +6043,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>6</v>
@@ -6048,19 +6054,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="C209" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C209" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="E209" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>6</v>
@@ -6077,10 +6083,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>6</v>
@@ -6097,10 +6103,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>6</v>
@@ -6117,10 +6123,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>6</v>
@@ -6137,10 +6143,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>6</v>
@@ -6157,10 +6163,10 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>6</v>
@@ -6177,10 +6183,10 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>6</v>
@@ -6188,19 +6194,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>6</v>
@@ -6217,10 +6223,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>6</v>
@@ -6237,10 +6243,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>6</v>
@@ -6257,10 +6263,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>6</v>
@@ -6277,12 +6283,32 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E220" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E221" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F220" s="1" t="s">
+      <c r="F221" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -256,6 +256,24 @@
     <t>IDM BROWNIS CHOCIP35</t>
   </si>
   <si>
+    <t>20144193</t>
+  </si>
+  <si>
+    <t>LD.LIMA CB CKLT 45G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20144120</t>
+  </si>
+  <si>
+    <t>WC THN CKE CHOCO 33G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>10000360</t>
   </si>
   <si>
@@ -286,15 +304,6 @@
     <t>NISSIN WFR CHOCO 570</t>
   </si>
   <si>
-    <t>20128683</t>
-  </si>
-  <si>
-    <t>TANGO WFLE CHO HZL63</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>10038628</t>
   </si>
   <si>
@@ -322,9 +331,6 @@
     <t>IMPERIAL BLUBERRY108</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>20139973</t>
   </si>
   <si>
@@ -403,7 +409,7 @@
     <t>20091225</t>
   </si>
   <si>
-    <t>OVLTNE CHO BISC 104G</t>
+    <t>OVLTNE CO BISC 104 G</t>
   </si>
   <si>
     <t>13</t>
@@ -586,12 +592,6 @@
     <t>DELFI KRICE SWET64.8</t>
   </si>
   <si>
-    <t>20139081</t>
-  </si>
-  <si>
-    <t>REGAL CHO MARIE 64G</t>
-  </si>
-  <si>
     <t>20130007</t>
   </si>
   <si>
@@ -697,7 +697,7 @@
     <t>20143290</t>
   </si>
   <si>
-    <t>NISSIN WFR CHCLAVA 5</t>
+    <t>NISSIN WFR C.LV 50 G</t>
   </si>
   <si>
     <t>23</t>
@@ -2603,10 +2603,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -2614,19 +2614,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2634,10 +2634,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2646,7 +2646,7 @@
         <v>68</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2666,7 +2666,7 @@
         <v>68</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2686,7 +2686,7 @@
         <v>68</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2694,19 +2694,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2714,22 +2714,22 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2743,30 +2743,30 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2774,19 +2774,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2803,10 +2803,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2823,33 +2823,33 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2863,10 +2863,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2874,19 +2874,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2903,13 +2903,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2923,30 +2923,30 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="E53" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2963,10 +2963,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2983,10 +2983,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -3003,13 +3003,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,30 +3023,30 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="E58" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -3063,10 +3063,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -3083,10 +3083,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -3103,10 +3103,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>6</v>
@@ -3114,19 +3114,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>6</v>
@@ -3143,10 +3143,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -3163,10 +3163,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -3183,10 +3183,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -3203,10 +3203,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -3214,19 +3214,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -3243,10 +3243,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -3263,10 +3263,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -3283,10 +3283,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -3294,19 +3294,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -3323,10 +3323,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -3343,10 +3343,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -3354,19 +3354,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>6</v>
@@ -3383,13 +3383,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3403,10 +3403,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
@@ -3423,10 +3423,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>13</v>
@@ -3443,10 +3443,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>13</v>
@@ -3463,10 +3463,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>13</v>
@@ -3483,33 +3483,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="E81" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3523,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>13</v>
@@ -3543,13 +3543,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3563,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -3583,10 +3583,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -3603,7 +3603,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>65</v>
@@ -4386,7 +4386,7 @@
         <v>263</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>6</v>
@@ -4406,7 +4406,7 @@
         <v>263</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>6</v>
@@ -4586,7 +4586,7 @@
         <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>6</v>
@@ -4606,7 +4606,7 @@
         <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>6</v>
@@ -4689,7 +4689,7 @@
         <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -5606,7 +5606,7 @@
         <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>6</v>
@@ -5629,7 +5629,7 @@
         <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5789,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5809,7 +5809,7 @@
         <v>5</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5829,7 +5829,7 @@
         <v>9</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5849,7 +5849,7 @@
         <v>12</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5969,7 +5969,7 @@
         <v>5</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">

--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,29 +11,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="501">
   <si>
     <t/>
   </si>
   <si>
+    <t>20144248</t>
+  </si>
+  <si>
+    <t>NISSIN WAFER CHOC325</t>
+  </si>
+  <si>
+    <t>BIS05D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20025592</t>
   </si>
   <si>
     <t>K/G WAFER CLASSIC350</t>
   </si>
   <si>
-    <t>BIS05D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20013332</t>
   </si>
   <si>
@@ -190,25 +196,43 @@
     <t>KTST BGLN GT BUTER45</t>
   </si>
   <si>
+    <t>20144170</t>
+  </si>
+  <si>
+    <t>KT CRSN/B CHEESE 40</t>
+  </si>
+  <si>
+    <t>20144169</t>
+  </si>
+  <si>
+    <t>KT CRSN/B SLT CRML40</t>
+  </si>
+  <si>
     <t>20048790</t>
   </si>
   <si>
     <t>OREO MINI CHOCO 58.4</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20048791</t>
   </si>
   <si>
     <t>OREO MINI VANLA 58.4</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>20137583</t>
   </si>
   <si>
     <t>IDM BROWNIS CHEESE35</t>
   </si>
   <si>
-    <t>7</t>
+    <t>9</t>
   </si>
   <si>
     <t>20143735</t>
@@ -217,7 +241,7 @@
     <t>IDM BRWNS CRSPY MW35</t>
   </si>
   <si>
-    <t>8</t>
+    <t>10</t>
   </si>
   <si>
     <t>20132494</t>
@@ -262,18 +286,12 @@
     <t>LD.LIMA CB CKLT 45G</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20144120</t>
   </si>
   <si>
     <t>WC THN CKE CHOCO 33G</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>10000360</t>
   </si>
   <si>
@@ -406,6 +424,12 @@
     <t>LEXUS SANDW CKLT 76G</t>
   </si>
   <si>
+    <t>20144232</t>
+  </si>
+  <si>
+    <t>MNCHYS CHCLPA SNDW90</t>
+  </si>
+  <si>
     <t>20091225</t>
   </si>
   <si>
@@ -550,13 +574,13 @@
     <t>20015337</t>
   </si>
   <si>
-    <t>LEXUS SANDW COKL 190</t>
+    <t>LXS SDW MFSND COK190</t>
   </si>
   <si>
     <t>20015338</t>
   </si>
   <si>
-    <t>LEXUS SANDW CHSE 190</t>
+    <t>LXS SDW MFSND CHS190</t>
   </si>
   <si>
     <t>10036899</t>
@@ -1102,7 +1126,7 @@
     <t>NUTELLA B-READY/F 22</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
+    <t>RT,(E-0.5B)</t>
   </si>
   <si>
     <t>10002246</t>
@@ -1882,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1926,18 +1950,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -1946,18 +1970,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -1966,18 +1990,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -1986,30 +2010,30 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2023,13 +2047,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2043,13 +2067,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,13 +2087,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2083,13 +2107,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2103,13 +2127,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,13 +2147,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2143,13 +2167,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2163,13 +2187,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,13 +2207,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2203,13 +2227,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,13 +2247,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2243,13 +2267,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2263,13 +2287,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2283,13 +2307,13 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2303,13 +2327,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2323,33 +2347,33 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,13 +2387,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2383,13 +2407,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,13 +2427,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2423,13 +2447,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2443,53 +2467,53 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,133 +2527,133 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,13 +2667,13 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,13 +2687,13 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,13 +2707,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,13 +2727,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2723,13 +2747,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2743,73 +2767,73 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,13 +2847,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,173 +2867,173 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,13 +3047,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3043,173 +3067,173 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3223,233 +3247,233 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3463,13 +3487,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3483,13 +3507,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3503,93 +3527,93 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3603,13 +3627,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3623,373 +3647,373 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4003,13 +4027,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4023,13 +4047,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4043,13 +4067,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4063,93 +4087,93 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4163,13 +4187,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4183,13 +4207,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4203,13 +4227,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4223,93 +4247,93 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4323,13 +4347,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4343,13 +4367,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4363,13 +4387,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4383,13 +4407,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4403,13 +4427,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4423,93 +4447,93 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4523,13 +4547,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4543,13 +4567,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4563,13 +4587,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4583,13 +4607,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4603,13 +4627,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4623,93 +4647,93 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4723,13 +4747,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4743,93 +4767,93 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4843,253 +4867,253 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5103,253 +5127,253 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>363</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5363,173 +5387,173 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5543,13 +5567,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5563,13 +5587,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5583,13 +5607,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5603,13 +5627,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5623,533 +5647,533 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>419</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F192" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>459</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E210" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B212" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E213" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6163,13 +6187,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6183,13 +6207,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6203,93 +6227,93 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="C220" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C220" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="E220" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6303,13 +6327,93 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
